--- a/docs/translations-v3.xlsx
+++ b/docs/translations-v3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E716"/>
+  <dimension ref="A1:E719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -19734,6 +19734,87 @@
       <c r="E716" s="4" t="inlineStr">
         <is>
           <t>العودة إلى الصفحة الرئيسية</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>knowledge.category.events (pill/chip)</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>رویدادها</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>События</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>الفعاليات</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>knowledge.category.articles (pill/chip)</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>مقالات علمی تخصصی</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Scientific articles</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Научные статьи</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>مقالات علمية متخصصة</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>knowledge.category.news (pill/chip)</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>اخبار علمی</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Scientific news</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Научные новости</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>أخبار علمية</t>
         </is>
       </c>
     </row>
@@ -34322,7 +34403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -34367,16 +34448,24 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>طراحی اپلیکیشن تشخیص اسکناس برای بانک مرکزی</t>
+          <t>طراحی اپلیکیشن نما تشخیص دنو اسکناس بانک مرکزی</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>A banknote recognition app for the Central Bank</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
+          <t>Designing «Nama», a banknote denomination recognition app for the Central Bank</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>«Нама»: приложение для распознавания номинала банкнот для Центрального банка</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>تصميم تطبيق «نما» للتعرف على فئات الأوراق النقدية للبنك المركزي</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -34386,16 +34475,24 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>معرفی پروژه طراحی اپلیکیشن موبایل تشخیص اسکناس برای بانک مرکزی. (متن کامل را ارسال کنید.)</t>
+          <t>نما یک اپلیکیشن هوشمند برای تشخیص دنو اسکناس‌های رایج کشور است که با هدف تسهیل تشخیص دقیق دنو انواع اسکناس و دسترسی سریع به اطلاعات به‌صورت آفلاین طراحی شده است. کاربران می‌توانند با استفاده از این اپلیکیشن، اسکناس موردنظر را اسکن کرده یا از گالری اپ انتخاب نمایند و مشخصات و ویژگی‌های آن را مشاهده کنند.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>About our project designing a mobile banknote recognition app for the Central Bank. (Full text to be supplied.)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
+          <t>Nama is a smart app that recognizes the denominations of the country's banknotes in circulation. It was designed to make identifying every banknote accurate and easy, with fast access to information even offline. Users scan a banknote, or pick a photo from the app's gallery, and see its details and features.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>«Нама» — умное приложение для распознавания номинала банкнот, находящихся в обращении в стране. Оно создано, чтобы точно определять любую банкноту и быстро получать информацию даже без интернета. Пользователь сканирует банкноту или выбирает снимок из галереи приложения и видит её характеристики и особенности.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>«نما» تطبيق ذكي للتعرف على فئات الأوراق النقدية المتداولة في البلاد، صُمّم لتسهيل التعرف الدقيق على فئة كل ورقة نقدية والوصول السريع إلى المعلومات دون الحاجة إلى اتصال بالإنترنت. يمكن للمستخدم مسح الورقة النقدية أو اختيار صورتها من معرض التطبيق والاطلاع على مواصفاتها وخصائصها.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -34467,12 +34564,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ERP vs CRM: a complete guide to choosing enterprise solutions that raise productivity</t>
+          <t>ERP vs CRM: what's the difference? A complete guide to choosing enterprise solutions that raise productivity</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ERP и CRM: в чем разница и как выбрать корпоративное решение</t>
+          <t>ERP и CRM: в чём разница? Полное руководство по выбору корпоративных решений для роста производительности</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -34489,22 +34586,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ERP فرایندهای داخلی سازمان مثل مالی، انبار و تولید را یکپارچه می‌کند و CRM روی ارتباط با مشتری تمرکز دارد. این راهنما کمک می‌کند بدانید کدام را و به چه ترتیبی نیاز دارید.</t>
+          <t>در سازمان‌های امروزی، مدیریت اطلاعات و فرایندها بدون راهکارهای نرم‌افزاری یکپارچه به‌مرور پیچیده‌تر می‌شود. ERP بر مدیریت منابع و فرایندهای داخلی سازمان تمرکز دارد، در حالی که CRM ارتباط با مشتری و مدیریت چرخه فروش را پوشش می‌دهد.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ERP connects an organization's internal processes such as finance, inventory and production, while CRM focuses on customer relationships. This guide helps you decide which one you need, and in what order.</t>
+          <t>Without integrated software, managing information and processes gets harder over time. ERP focuses on managing an organization's resources and internal processes, while CRM covers customer relationships and the sales cycle.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ERP объединяет внутренние процессы организации — финансы, склад и производство, а CRM сосредоточена на отношениях с клиентами. Это руководство поможет понять, что нужно вашей организации и в каком порядке.</t>
+          <t>Без единых программных решений управлять информацией и процессами со временем всё сложнее. ERP сосредоточена на управлении ресурсами и внутренними процессами организации, а CRM — на отношениях с клиентами и цикле продаж.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>يكامل ERP العمليات الداخلية للمؤسسة مثل المالية والمخازن والإنتاج، بينما يركز CRM على العلاقة مع العملاء. يساعدك هذا الدليل على معرفة ما تحتاجه مؤسستك وبأي ترتيب.</t>
+          <t>من دون حلول برمجية متكاملة تصبح إدارة المعلومات والعمليات أكثر تعقيدًا مع الوقت. يركّز ERP على إدارة موارد المؤسسة وعملياتها الداخلية، بينما يغطي CRM العلاقة مع العملاء ودورة المبيعات.</t>
         </is>
       </c>
     </row>
@@ -34751,10 +34848,26 @@
           <t>financial-software.draft</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -34870,10 +34983,469 @@
           <t>user-training.draft</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>draft: true (hidden in ver4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>banknote-recognition-app.intro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>«نما» با تکیه بر فناوری‌های نوین، با مدل هوش مصنوعی آفلاین، تجربه‌ای ساده، سریع و قابل اعتماد برای شناسایی اسکناس و معرفی دنو در اختیار کاربران قرار می‌دهد.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Built on modern technology and an offline AI model, «Nama» gives users a simple, fast and reliable way to recognize banknotes and their denominations.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Опираясь на современные технологии и офлайн-модель искусственного интеллекта, «Нама» даёт пользователям простой, быстрый и надёжный способ распознавать банкноты и их номинал.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>يعتمد «نما» على أحدث التقنيات ونموذج ذكاء اصطناعي يعمل دون اتصال، ليقدّم للمستخدمين طريقة بسيطة وسريعة وموثوقة للتعرف على الأوراق النقدية وفئاتها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cyber-erp-1405-redesign.title</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CYBER ERP در ۱۴۰۵؛ بازطراحی تجربه و ارائه نسل جدید ERP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CYBER ERP in 1405: a redesigned experience and a new generation of ERP</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CYBER ERP в 1405 году: новый пользовательский опыт и новое поколение ERP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CYBER ERP في ١٤٠٥: تجربة مُعاد تصميمها وجيل جديد من ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cyber-erp-1405-redesign.summary</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>در سال ۱۴۰۵، CYBER ERP با رویکردی تازه بازطراحی و به‌روزرسانی شد تا تجربه‌ای مدرن‌تر، یکپارچه‌تر و کارآمدتر برای مدیریت سازمان ارائه دهد. این بازطراحی با تمرکز بر بهبود تجربه کاربری، دسترسی ساده‌تر به اطلاعات و هماهنگی بیشتر میان فرایندها و ماژول‌های سازمان انجام شده است.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>In 1405, CYBER ERP was redesigned and updated with a fresh approach, to give organizations a more modern, more integrated and more efficient way to run their business. The redesign focuses on a better user experience, simpler access to information and closer coordination between processes and modules.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>В 1405 году CYBER ERP получила новый дизайн и обновление, чтобы управление организацией стало более современным, единым и эффективным. Редизайн сосредоточен на улучшении пользовательского опыта, более простом доступе к информации и лучшей согласованности процессов и модулей.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>في عام ١٤٠٥ أُعيد تصميم CYBER ERP وتحديثه بنهج جديد، ليقدّم تجربة أحدث وأكثر تكاملًا وكفاءة في إدارة المؤسسة. ركّزت إعادة التصميم على تحسين تجربة المستخدم، وتسهيل الوصول إلى المعلومات، وزيادة التنسيق بين العمليات والوحدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features.title</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CyberERP نسل جدید چه ویژگی‌هایی اضافه شده</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>What's new in next-generation CyberERP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Что нового в CyberERP нового поколения</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ما الجديد في الجيل الجديد من CyberERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features.summary</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>بازطراحی رابط کاربری با تمرکز بر سادگی، سرعت دسترسی و کاهش پیچیدگی در کار با ماژول‌ها و فرایندهای سازمانی؛ استفاده از AI و تحلیل داده برای ارائه گزارش‌های هوشمند؛ و داشبوردهای لحظه‌ای برای پایش عملکرد سازمان.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A redesigned interface that is simpler, faster to navigate and less complex to work with; AI and data analysis for smart reports; and real-time dashboards to monitor how the organization is performing.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Обновлённый интерфейс — проще, быстрее и понятнее в работе с модулями и процессами; искусственный интеллект и анализ данных для умных отчётов; панели в реальном времени для контроля работы организации.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>واجهة مستخدم مُعاد تصميمها أبسط وأسرع وأقل تعقيدًا في العمل مع الوحدات والعمليات؛ والذكاء الاصطناعي وتحليل البيانات لتقارير ذكية؛ ولوحات معلومات لحظية لمتابعة أداء المؤسسة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features.body.1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>بازطراحی رابط کاربری با تمرکز بر سادگی، سرعت دسترسی و کاهش پیچیدگی در کار با ماژول‌ها و فرایندهای سازمانی.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A redesigned user interface focused on simplicity, faster access and less complexity when working with modules and business processes.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Обновлённый пользовательский интерфейс: простота, быстрый доступ и меньше сложностей при работе с модулями и бизнес-процессами.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>إعادة تصميم واجهة المستخدم مع التركيز على البساطة وسرعة الوصول وتقليل التعقيد عند العمل مع الوحدات وعمليات المؤسسة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features.body.2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>استفاده از AI و تحلیل داده برای استخراج بینش از اطلاعات، ارائه گزارش‌های هوشمند و کمک به مدیران در تصمیم‌گیری سریع‌تر و دقیق‌تر.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AI and data analysis that turn information into insight, deliver smart reports and help managers make faster, more accurate decisions.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Искусственный интеллект и анализ данных, которые превращают информацию в выводы, формируют умные отчёты и помогают руководителям принимать решения быстрее и точнее.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>استخدام الذكاء الاصطناعي وتحليل البيانات لاستخلاص الرؤى من المعلومات، وتقديم تقارير ذكية، ومساعدة المديرين على اتخاذ قرارات أسرع وأدق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features.body.3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ارائه تصویری لحظه‌ای از عملکرد سازمان با داشبوردها و شاخص‌های مدیریتی، برای پایش عملکرد و تصمیم‌گیری مبتنی بر داده.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A real-time picture of the organization's performance through dashboards and management indicators, for monitoring and data-driven decisions.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Картина работы организации в реальном времени: панели и управленческие показатели для контроля результатов и решений на основе данных.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>صورة لحظية عن أداء المؤسسة من خلال لوحات المعلومات ومؤشرات الإدارة، لمتابعة الأداء واتخاذ قرارات قائمة على البيانات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>erp-future.title</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>آینده ERP به کدام سمت می‌رود؟</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Where is ERP heading?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Куда движется ERP?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>إلى أين يتجه ERP؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>erp-future.summary</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>مسیر ERP از «ثبت اطلاعات» به «درک اطلاعات و کمک به تصمیم‌گیری» در حال حرکت است. در آینده، سازمان‌ها به جای اینکه صرفاً از ERP برای مشاهده اتفاقات گذشته استفاده کنند، انتظار خواهند داشت سیستم بتواند روندها را شناسایی کند، هشدارهای هوشمند ارائه دهد و در پیش‌بینی اتفاقات آینده به مدیران کمک کند.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ERP is moving from "recording information" to "understanding information and supporting decisions". Instead of using ERP only to look back at what happened, organizations will expect the system to spot trends, raise smart alerts and help managers anticipate what comes next.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ERP переходит от «учёта информации» к «пониманию информации и поддержке решений». Организации будут ждать от системы не только отчётов о прошлом: она должна выявлять тенденции, выдавать умные предупреждения и помогать руководителям прогнозировать будущее.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ينتقل ERP من «تسجيل المعلومات» إلى «فهم المعلومات ودعم اتخاذ القرار». ففي المستقبل لن تكتفي المؤسسات باستخدام ERP لمراجعة ما حدث، بل ستتوقع من النظام أن يرصد الاتجاهات ويقدّم تنبيهات ذكية ويساعد المديرين على توقّع ما سيحدث.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>erp-trends-1405.title</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>مهم‌ترین روندهای ERP در سال ۱۴۰۵</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The top ERP trends of 1405</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Главные тренды ERP в 1405 году</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>أهم اتجاهات ERP في عام ١٤٠٥</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>erp-trends-1405.summary</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>یکی از مهم‌ترین تغییرات ERP، ورود هوش مصنوعی به فرایندهای سازمانی است. AI می‌تواند با تحلیل داده‌های تاریخی و لحظه‌ای، الگوها و ناهنجاری‌ها را شناسایی کرده، گزارش‌های مدیریتی تولید کند و حتی در پیش‌بینی تقاضا، جریان نقدینگی، موجودی و عملکرد سازمان نقش داشته باشد.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>One of the biggest changes in ERP is artificial intelligence entering business processes. By analysing historical and real-time data, AI can spot patterns and anomalies, produce management reports and even help forecast demand, cash flow, inventory and company performance.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Одно из главных изменений в ERP — приход искусственного интеллекта в бизнес-процессы. Анализируя исторические и текущие данные, ИИ находит закономерности и отклонения, готовит управленческие отчёты и даже помогает прогнозировать спрос, денежный поток, запасы и результаты работы организации.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>من أهم التغيرات في ERP دخول الذكاء الاصطناعي إلى عمليات المؤسسة. فمن خلال تحليل البيانات التاريخية واللحظية، يستطيع الذكاء الاصطناعي رصد الأنماط والحالات الشاذة، وإعداد تقارير إدارية، بل والمساعدة في توقّع الطلب والتدفق النقدي والمخزون وأداء المؤسسة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>erp-vs-crm.body (Markdown)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>در سازمان‌های امروزی، مدیریت اطلاعات و فرایندها بدون استفاده از راهکارهای نرم‌افزاری یکپارچه، به‌مرور پیچیده‌تر می‌شود. ERP و CRM دو مورد از مهم‌ترین راهکارهای سازمانی هستند که هرکدام با هدف متفاوتی طراحی شده‌اند؛ ERP بر مدیریت منابع و فرایندهای داخلی سازمان تمرکز دارد، در حالی که CRM ارتباط با مشتری و مدیریت چرخه فروش را پوشش می‌دهد.
+شناخت تفاوت ERP و CRM به سازمان کمک می‌کند متناسب با نیازهای واقعی خود، راهکار مناسب را انتخاب کند و در صورت نیاز، این دو سیستم را در کنار یکدیگر به کار گیرد.
+## ERP چیست؟
+ERP یا Enterprise Resource Planning یک سیستم یکپارچه برای مدیریت و هماهنگی منابع، اطلاعات و فرایندهای اصلی سازمان است. ERP بخش‌های مختلف سازمان را در یک بستر مشترک به یکدیگر متصل می‌کند تا اطلاعات میان واحدها به‌صورت یکپارچه جریان داشته باشد.
+ماژول‌هایی مانند مالی و حسابداری، منابع انسانی، فروش، خرید، انبار، تولید، زنجیره تأمین، نگهداری و تعمیرات و مدیریت پروژه می‌توانند در یک اکوسیستم ERP قرار بگیرند.
+برای مثال، ثبت یک سفارش فروش می‌تواند به‌صورت یکپارچه روی موجودی انبار، برنامه‌ریزی تأمین، حسابداری و گزارش‌های مدیریتی اثر بگذارد. به این ترتیب، سازمان به جای استفاده از اطلاعات پراکنده، تصویری یکپارچه از وضعیت خود خواهد داشت.
+## CRM چیست؟
+CRM یا Customer Relationship Management به معنای مدیریت ارتباط با مشتری است و تمرکز اصلی آن بر شناخت، جذب، حفظ و توسعه ارتباط با مشتریان و مخاطبان سازمان قرار دارد.
+CRM اطلاعاتی مانند مشخصات مشتری، سوابق تماس، فرصت‌های فروش، درخواست‌ها، مذاکرات، قراردادها و تعاملات مشتری را مدیریت می‌کند و به تیم‌های فروش و بازاریابی کمک می‌کند چرخه ارتباط با مشتری را بهتر مدیریت کنند.
+برای مثال، تیم فروش می‌تواند مشاهده کند یک مشتری در چه مرحله‌ای از فرایند خرید قرار دارد، چه تعاملاتی با سازمان داشته و چه اقدام بعدی باید انجام شود.
+## تفاوت اصلی ERP و CRM در چیست؟
+اگر بخواهیم تفاوت این دو سیستم را بسیار ساده بیان کنیم:
+&gt; CRM بیشتر بر «مشتری و ارتباط با او» تمرکز دارد؛ ERP بر «کل سازمان و منابع آن».
+| ERP | CRM |
+| --- | --- |
+| مدیریت کل سازمان | مدیریت ارتباط با مشتری |
+| تمرکز بر فرایندهای داخلی | تمرکز بر مشتری و فروش |
+| مالی و حسابداری | مدیریت سرنخ‌ها |
+| منابع انسانی | مدیریت فرصت‌های فروش |
+| تولید | بازاریابی |
+| خرید و تأمین | خدمات مشتری |
+| انبار و لجستیک | سوابق تعاملات مشتری |
+| گزارش‌دهی سازمانی | تحلیل عملکرد فروش |
+البته این به معنی جدا بودن کامل این دو سیستم نیست. در یک معماری سازمانی مدرن، CRM و ERP باید بتوانند با یکدیگر تبادل اطلاعات داشته باشند.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>In today's organizations, managing information and processes without integrated software gets more complex over time. ERP and CRM are two of the most important enterprise solutions, and each was designed for a different purpose: ERP focuses on managing the organization's resources and internal processes, while CRM covers customer relationships and the sales cycle.
+Knowing the difference between ERP and CRM helps an organization choose the solution that fits its real needs and, where necessary, use the two systems side by side.
+## What is ERP?
+ERP, or Enterprise Resource Planning, is an integrated system for managing and coordinating an organization's resources, information and core processes. ERP connects the different parts of the organization on one shared platform, so information flows between departments in an integrated way.
+Modules such as finance and accounting, human resources, sales, purchasing, warehouse, production, supply chain, maintenance and project management can all be part of one ERP ecosystem.
+For example, entering a sales order can automatically update warehouse stock, supply planning, accounting and management reports. Instead of working with scattered information, the organization gets one integrated picture of where it stands.
+## What is CRM?
+CRM, or Customer Relationship Management, is about managing the relationship with customers. Its main focus is understanding, winning, keeping and growing relationships with the organization's customers and audiences.
+CRM manages information such as customer details, contact history, sales opportunities, requests, negotiations, contracts and customer interactions, and helps sales and marketing teams manage the customer relationship cycle better.
+For example, the sales team can see which stage of the buying process a customer is at, what interactions they have had with the organization and what the next step should be.
+## What is the main difference between ERP and CRM?
+Put very simply:
+&gt; CRM focuses on "the customer and the relationship with them"; ERP on "the whole organization and its resources".
+| ERP | CRM |
+| --- | --- |
+| Managing the whole organization | Managing customer relationships |
+| Focus on internal processes | Focus on customers and sales |
+| Finance and accounting | Lead management |
+| Human resources | Sales opportunity management |
+| Production | Marketing |
+| Purchasing and supply | Customer service |
+| Warehouse and logistics | Customer interaction history |
+| Organization-wide reporting | Sales performance analysis |
+This does not mean the two systems are completely separate. In a modern enterprise architecture, CRM and ERP should be able to exchange information with each other.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>В современных организациях управлять информацией и процессами без единых программных решений со временем становится всё сложнее. ERP и CRM — два важнейших корпоративных решения, и каждое создано для своей задачи: ERP сосредоточена на управлении ресурсами и внутренними процессами организации, а CRM охватывает отношения с клиентами и цикл продаж.
+Понимание разницы между ERP и CRM помогает организации выбрать решение, соответствующее её реальным потребностям, и при необходимости использовать обе системы вместе.
+## Что такое ERP?
+ERP (Enterprise Resource Planning, планирование ресурсов предприятия) — это единая система для управления и координации ресурсов, информации и основных процессов организации. ERP связывает разные подразделения на общей платформе, чтобы информация между ними передавалась единым потоком.
+В экосистему ERP могут входить такие модули, как финансы и бухгалтерия, управление персоналом, продажи, закупки, склад, производство, цепочка поставок, техническое обслуживание и ремонт, а также управление проектами.
+Например, оформление заказа на продажу может сразу отразиться на складских остатках, планировании поставок, бухгалтерии и управленческих отчётах. Вместо разрозненных данных организация получает единую картину своего состояния.
+## Что такое CRM?
+CRM (Customer Relationship Management) — это управление отношениями с клиентами. Её главная задача — понимать, привлекать, удерживать и развивать отношения с клиентами и аудиторией организации.
+CRM управляет такой информацией, как данные клиентов, история контактов, возможности продаж, запросы, переговоры, договоры и взаимодействия с клиентами, и помогает отделам продаж и маркетинга лучше вести цикл работы с клиентом.
+Например, отдел продаж видит, на каком этапе покупки находится клиент, как он взаимодействовал с организацией и каким должен быть следующий шаг.
+## В чём главное различие между ERP и CRM?
+Если сказать совсем просто:
+&gt; CRM сосредоточена на «клиенте и отношениях с ним», ERP — на «всей организации и её ресурсах».
+| ERP | CRM |
+| --- | --- |
+| Управление всей организацией | Управление отношениями с клиентами |
+| Фокус на внутренних процессах | Фокус на клиентах и продажах |
+| Финансы и бухгалтерия | Управление лидами |
+| Управление персоналом | Управление возможностями продаж |
+| Производство | Маркетинг |
+| Закупки и снабжение | Обслуживание клиентов |
+| Склад и логистика | История взаимодействий с клиентами |
+| Отчётность по всей организации | Анализ эффективности продаж |
+Это не значит, что две системы полностью разделены. В современной корпоративной архитектуре CRM и ERP должны обмениваться информацией друг с другом.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>في المؤسسات اليوم، تصبح إدارة المعلومات والعمليات من دون حلول برمجية متكاملة أكثر تعقيدًا مع مرور الوقت. ويُعدّ ERP وCRM من أهم الحلول المؤسسية، وقد صُمّم كلٌّ منهما لهدف مختلف؛ إذ يركّز ERP على إدارة موارد المؤسسة وعملياتها الداخلية، بينما يغطي CRM العلاقة مع العملاء وإدارة دورة المبيعات.
+إن فهم الفرق بين ERP وCRM يساعد المؤسسة على اختيار الحل المناسب لاحتياجاتها الفعلية، واستخدام النظامين معًا عند الحاجة.
+## ما هو ERP؟
+ERP أو Enterprise Resource Planning (تخطيط موارد المؤسسات) نظام متكامل لإدارة موارد المؤسسة ومعلوماتها وعملياتها الأساسية وتنسيقها. يربط ERP أقسام المؤسسة المختلفة على منصة مشتركة، لتتدفق المعلومات بين الوحدات بشكل متكامل.
+ويمكن أن تضم منظومة ERP وحدات مثل المالية والمحاسبة، والموارد البشرية، والمبيعات، والمشتريات، والمستودعات، والإنتاج، وسلسلة الإمداد، والصيانة والإصلاح، وإدارة المشاريع.
+فعلى سبيل المثال، يمكن لتسجيل أمر بيع واحد أن يؤثر تلقائيًا في مخزون المستودع وتخطيط الإمداد والمحاسبة والتقارير الإدارية. وبذلك تحصل المؤسسة على صورة متكاملة عن وضعها بدلًا من معلومات متفرقة.
+## ما هو CRM؟
+CRM أو Customer Relationship Management يعني إدارة العلاقة مع العملاء، ويتمحور حول فهم العملاء والجمهور واستقطابهم والحفاظ عليهم وتطوير العلاقة معهم.
+يدير CRM معلومات مثل بيانات العملاء، وسجل الاتصالات، وفرص البيع، والطلبات، والمفاوضات، والعقود، والتفاعلات مع العملاء، ويساعد فرق المبيعات والتسويق على إدارة دورة العلاقة مع العميل بشكل أفضل.
+فعلى سبيل المثال، يستطيع فريق المبيعات أن يرى في أي مرحلة من الشراء يوجد العميل، وما التفاعلات التي جرت بينه وبين المؤسسة، وما الخطوة التالية المطلوبة.
+## ما الفرق الأساسي بين ERP وCRM؟
+إذا أردنا التعبير عن الفرق بين النظامين ببساطة شديدة:
+&gt; يركّز CRM على «العميل والعلاقة معه»، بينما يركّز ERP على «المؤسسة كلها ومواردها».
+| ERP | CRM |
+| --- | --- |
+| إدارة المؤسسة كلها | إدارة العلاقة مع العملاء |
+| التركيز على العمليات الداخلية | التركيز على العملاء والمبيعات |
+| المالية والمحاسبة | إدارة العملاء المحتملين |
+| الموارد البشرية | إدارة فرص البيع |
+| الإنتاج | التسويق |
+| المشتريات والإمداد | خدمة العملاء |
+| المستودعات والخدمات اللوجستية | سجل التفاعلات مع العملاء |
+| التقارير على مستوى المؤسسة | تحليل أداء المبيعات |
+ولا يعني ذلك أن النظامين منفصلان تمامًا؛ ففي البنية المؤسسية الحديثة يجب أن يتمكن CRM وERP من تبادل المعلومات فيما بينهما.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34886,7 +35458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -36894,6 +37466,114 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>articles.cyber-erp-1405-redesign</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>بازطراحی-cyber-erp-1405</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>cyber-erp-1405-redesign</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>редизайн-cyber-erp-1405</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>إعادة-تصميم-cyber-erp-1405</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>articles.next-gen-cybererp-features</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ویژگی-های-نسل-جدید-cybererp</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>next-gen-cybererp-features</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>новое-поколение-cybererp</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>الجيل-الجديد-من-cybererp</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>articles.erp-future</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>آینده-erp</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>erp-future</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>будущее-erp</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>مستقبل-erp</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>articles.erp-trends-1405</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>روندهای-erp-1405</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>erp-trends-1405</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>тренды-erp-1405</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>اتجاهات-erp-1405</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
